--- a/光伏配储项目/电价数据/2026/潮阳站.xlsx
+++ b/光伏配储项目/电价数据/2026/潮阳站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.3165</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.33508</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.31752</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.31762</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.31768</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.31569</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.31667</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.31379</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.31364</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.31553</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.31539</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.31507</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.31731</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.31756</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.31742</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.31377</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30798</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.27594</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29051</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.26945</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.27695</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.26645</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.25367</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.17296</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.17397</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.19496</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.2827</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.32678</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.33247</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.3434700000000001</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07318000000000001</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.24394</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.04364</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.1709</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.26495</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25219</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.25681</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24147</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.33217</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.31499</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.27998</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.30239</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.31415</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.29931</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.29494</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.35885</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.40882</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.39195</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.01893</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.50116</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.31121</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.39155</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.54264</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.20391</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.0893</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.8512000000000001</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.0174</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.99663</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.7829400000000001</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.12226</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.44606</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.46684</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.4722</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.13547</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.41002</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.36288</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.47696</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.46639</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.39445</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.32385</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.3232</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.34323</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.33597</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.47359</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.31554</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.31406</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.31344</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.3139</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.32276</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.32251</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.32274</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.32379</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.31464</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.30639</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.30866</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.29066</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.27226</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.13501</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.21838</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.6534800000000001</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.6141799999999999</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.37883</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.29359</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.34594</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.29845</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.30499</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.44453</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.20029</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.29464</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.21046</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.11314</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.35253</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.34366</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.10483</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.31308</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.30563</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.75942</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.79244</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.7890199999999999</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.7900499999999999</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.36549</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.79977</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.83778</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.8636699999999999</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.02139</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.82221</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.60848</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.79423</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.39386</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.8220299999999999</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.7812899999999999</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.81514</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.5039399999999999</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.8406399999999999</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.32118</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.51105</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.41202</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.32967</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.31565</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.32417</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.32592</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.33133</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.33305</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.27328</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.27661</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.32623</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.29421</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.32527</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.31524</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.31388</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.31535</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.31255</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.31508</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.31024</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.30574</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.31075</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.30925</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.30931</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.30849</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.31145</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.31271</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.31307</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.36865</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.32981</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.32047</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.11177</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.16196</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.23212</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.30185</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.31403</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.05625</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.31306</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30848</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.27757</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.29502</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.7325900000000001</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.75705</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.7859700000000001</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29304</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.28239</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.19208</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.22272</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.27022</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.33685</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.44318</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.31637</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.06916</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.4583</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.51218</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.5143799999999999</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.51544</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.55524</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.53328</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.62991</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.40184</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.34179</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.70611</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.42416</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50317</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.50997</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.45741</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.6457000000000001</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.45835</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.39966</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.5981000000000001</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.35242</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.37181</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.47416</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.4341</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.47596</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.48012</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.44852</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.46591</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.50995</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.3311</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.32366</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.32143</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.31351</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.31556</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.31208</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.31418</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.31435</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.3117</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.31195</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.31229</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.31166</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.31248</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.31192</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.30102</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.31254</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.30415</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.31764</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.32268</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.32304</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.33173</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.44463</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.37595</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.35694</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.35448</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.48372</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.46722</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.06445000000000001</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.2949</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.78975</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.10468</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.10758</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.31594</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.14116</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.27227</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.30673</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>-0.03198</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.37898</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.30801</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.20046</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.14079</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>-0.04649</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.09887</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45064</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.32357</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.31189</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.3718399999999999</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.37064</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.6684600000000001</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.34666</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.30944</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50244</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.33886</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.30813</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.31271</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.30305</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.30437</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.30364</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.30918</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.30512</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.29981</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.26256</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>-0.00873</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.36322</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.36292</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31679</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31334</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.3182</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31453</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31976</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.30045</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31905</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.33351</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28949</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.29352</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14357</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.31533</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.02601</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.30331</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.29833</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.29375</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.31498</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.30333</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.40609</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.26465</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.25674</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.23927</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.10406</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.2679</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.02922</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26349</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30486</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32656</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34793</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.36255</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.36681</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.41334</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35614</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36751</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.36142</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.42467</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34248</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34282</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.3184</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.10556</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.29389</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.24805</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.25337</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.05894</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.09222</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32847</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.19643</v>
+      </c>
+      <c r="L122" t="n">
+        <v>-0.01439</v>
+      </c>
+      <c r="M122" t="n">
+        <v>-0.02794</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.25251</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.08604000000000001</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.3061</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.03588</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.25109</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.2191</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.19725</v>
+      </c>
+      <c r="W122" t="n">
+        <v>-0.01442</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.17934</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.25229</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.27336</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.20617</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.32243</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01012</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.2064</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04936</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.2757</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19407</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.01148</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06054</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05875</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.3238</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.31646</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.30307</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0.7099800000000001</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.30395</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31934</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.30173</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.06361</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.77119</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88749</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87038</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.6581</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5737899999999999</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.41693</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.40669</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39303</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.3538</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37812</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38844</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.39947</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37504</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32844</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32603</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44392</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.36492</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.39419</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.45181</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.50506</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.29415</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.44483</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.26458</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.5960599999999999</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32861</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.27988</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.30427</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29238</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.26715</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.30888</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.18172</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.29393</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.28961</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.31195</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.30497</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.30569</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.28619</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29363</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30791</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29543</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.3056</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.18426</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.26411</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.26394</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.27844</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.26369</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.28259</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.29356</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.31139</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.30928</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.30157</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.2954</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.3062</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.30656</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.31204</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.30603</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.30736</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.29321</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.3246</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.77181</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.30964</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.29895</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.29949</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.30464</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.29708</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.30206</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.29883</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.30025</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.30865</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.31061</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.29461</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.29507</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.29564</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.29719</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.20938</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.20537</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.29491</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.29568</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.2974</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.29921</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.29993</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.27964</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.08089</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>-0.01557</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.29273</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.29734</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.07936</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.30656</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30885</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30387</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>-0.01412</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31217</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>-0.00697</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.09093999999999999</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>-0.01233</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.27427</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.37902</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.01636</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.45098</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.09853000000000001</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>-0.01319</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.02973</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>-0.04889</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.01526</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>-0.01745</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>-0.01156</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>-0.009140000000000001</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>-0.04744</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>-0.03786</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>-0.03831</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>-0.03525</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>-0.03946</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.07587999999999999</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>-0.01062</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>-0.01656</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>-0.01124</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>-0.01297</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>-0.00155</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>-0.01755</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>-0.01188</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>-0.0116</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>-0.008710000000000001</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>-0.01372</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>-0.01106</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>-0.01074</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>-0.00941</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>-0.00891</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>-0.01272</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.08147</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>-0.01259</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.00172</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>-0.008750000000000001</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>-0.01073</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>-0.0128</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>-0.01055</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.21362</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>-0.01249</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>-0.01288</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>-0.01173</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>-0.0382</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-0.02822</v>
+      </c>
+      <c r="D126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F126" t="n">
+        <v>-0.02463</v>
+      </c>
+      <c r="G126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H126" t="n">
+        <v>-0.0301</v>
+      </c>
+      <c r="I126" t="n">
+        <v>-0.03667</v>
+      </c>
+      <c r="J126" t="n">
+        <v>-0.03796</v>
+      </c>
+      <c r="K126" t="n">
+        <v>-0.02431</v>
+      </c>
+      <c r="L126" t="n">
+        <v>-0.02026</v>
+      </c>
+      <c r="M126" t="n">
+        <v>-0.007719999999999999</v>
+      </c>
+      <c r="N126" t="n">
+        <v>-0.01703</v>
+      </c>
+      <c r="O126" t="n">
+        <v>-0.02175</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.09182</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>-0.00932</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.08927</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.04669</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.10303</v>
+      </c>
+      <c r="U126" t="n">
+        <v>-0.01646</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.10959</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.25361</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>-0.04457</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.03984</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.21157</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.25888</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.15142</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.23582</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.07762999999999999</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.15198</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.24886</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.00843</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.03202</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>-0.02753</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.28401</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.28678</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.2491</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.20724</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.31736</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.22238</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.06064</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.14546</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.00465</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.05542</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.19074</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.006719999999999999</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30071</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.0549</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.03902000000000001</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.08563</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.11897</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>-0.02851</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.04653</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.19966</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.04977</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.24162</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.25038</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>-0.02665</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.25662</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.03865</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.06733</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.09583</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.09245</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.09011</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.09193999999999999</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.08511000000000001</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.07140000000000001</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.11118</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.08979000000000001</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.07554000000000001</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.11692</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.08885</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.09117</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.20703</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>-0.01007</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.08952</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.28828</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.3078</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.10024</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.08362</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.29543</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.2378</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.06964000000000001</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.22804</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>-0.01706</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.07187</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.06423000000000001</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.03503</v>
+      </c>
+      <c r="F127" t="n">
+        <v>-0.02695</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.30598</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.05283</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.19258</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.03807</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.18975</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.02827</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.05586</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.06426000000000001</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.06251</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.07607999999999999</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.07467</v>
+      </c>
+      <c r="R127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S127" t="n">
+        <v>-0.04136</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.03482</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.03854</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.07326000000000001</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.04062</v>
+      </c>
+      <c r="X127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.19517</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.04104</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.01733</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.01646</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.03959</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.06901</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.1673</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.02624</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.14404</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.0299</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.24781</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>-0.0469</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>-0.01405</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.12708</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.05094</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.05445000000000001</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.28907</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.12123</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.24151</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.06192</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.1284</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.05615</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.05416</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.16945</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28238</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.1884</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.24727</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.21544</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.26626</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.24738</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.26457</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.20752</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.24255</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.26639</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.2553</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.23466</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.27526</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.26144</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.27387</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.29761</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.30395</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.28396</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.28618</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.3007</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.30619</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.30138</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.27496</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.27275</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.28471</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.27351</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.28783</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.30671</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.27394</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.28586</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.29467</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.39173</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.26727</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.26573</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.31726</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.28716</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.28944</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.25295</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.28385</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.29133</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.3161</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.34611</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.31133</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.30879</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.30844</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.30143</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.3039</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.30463</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.30591</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.33172</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.30743</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.30486</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.30757</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.30571</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.3011</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.29799</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.29756</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.30158</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.29596</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.29759</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.29596</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.29853</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.30386</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.3026</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.29283</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3028</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.29593</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.28817</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.30947</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28283</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.28609</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30352</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28538</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.3094</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28362</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.23322</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30241</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.28807</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.29657</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.29134</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.2796</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29994</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.29881</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31402</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31523</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30051</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.30334</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29504</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.2471</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.29549</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.28799</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.3048</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.29212</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.29123</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.30037</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32695</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32786</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.31855</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.37662</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33597</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.31713</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.3662</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.42735</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.29779</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.35286</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.32264</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.31534</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.31199</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31518</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.31499</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.31458</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.29217</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.30903</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.30908</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.30507</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.31061</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.31444</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.30617</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.29136</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.29586</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.28947</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.29438</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.29603</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.29962</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.30162</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.29668</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.29753</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.29734</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.31433</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.30979</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.29533</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.31111</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30662</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.2964</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.29809</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.29822</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.29336</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.34321</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.31005</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.29753</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.30645</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.39345</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.9710299999999999</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.40905</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.61797</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.38573</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.47176</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.49359</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.3786600000000001</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.4265</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.47983</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.38355</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.42084</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.39509</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.53011</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27822</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.31395</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.32547</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.26742</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.35519</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.19334</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.42466</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.19596</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.20394</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.4332</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.4123</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.39779</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.52008</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.41163</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.31705</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.41807</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.37693</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.42395</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.32828</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.12598</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.11287</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.33653</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.00792</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.36408</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.34788</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.02264</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.43493</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.42135</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>-0.00036</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.15569</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.6272799999999999</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.3839</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.2612</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.09859</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.46944</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>-0.01738</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.09881999999999999</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.05834</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.07703</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.24364</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>-0.02039</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.28764</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.04895</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>-0.02053</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.28272</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.18085</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.38583</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.27302</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.27629</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.27985</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.28013</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.19698</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.26991</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.27994</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.27682</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.26886</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.2763</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.19885</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29661</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.19616</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.16123</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.23893</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.27956</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.20003</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>8.999999999999999e-05</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.19589</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.20155</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.01859</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.20869</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.17474</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.16586</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.16936</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.20552</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.24006</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.29965</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.30342</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.2126</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.26558</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.30437</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.24685</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.30185</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.30062</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.24288</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>-0.01526</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.24465</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.22657</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.25892</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.22847</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.23218</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.20996</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.29758</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.19768</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.24014</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.22382</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.27193</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.23887</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.20215</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.19774</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.07252</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.18821</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.20059</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>-0.04784</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.23094</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.25687</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.15785</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.25024</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.27815</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.22923</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.2629</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.30244</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.30352</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.27382</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.3019</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.27426</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.28937</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.28897</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.31749</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.2775899999999999</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.2777</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.28927</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.21745</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.29334</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.20981</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.28417</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.2790899999999999</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.31597</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.0157</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.23936</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.31858</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.29451</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.32174</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.32271</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.28369</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.31759</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.00024</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.29159</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.28823</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.27639</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.31092</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.31139</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.28791</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.28685</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.29573</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.28535</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.28644</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.28751</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.27589</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.28638</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.29229</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.29182</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30767</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.28296</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.27644</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.28681</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.2949</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.27649</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.28688</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.27208</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.29286</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.30075</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30775</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30181</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.3122200000000001</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30636</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30731</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.30566</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31791</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37008</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.30815</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35906</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32304</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.30469</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.32217</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.32463</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.34234</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.32245</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.31726</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.33461</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.32966</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.32299</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.32716</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.39178</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.55899</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.52425</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.21293</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.29876</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.3825</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.33054</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.31716</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.33134</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.31437</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.33116</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.28776</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.31177</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33723</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.35124</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.32323</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30887</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.41304</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.31722</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.3141</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.31915</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.32517</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.31934</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.32729</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.35289</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.41114</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.3715</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.38907</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.34848</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32347</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.34657</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.37168</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.44548</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.50428</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.58665</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.55298</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.59884</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.73281</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.4227</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.38523</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.4646</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.39716</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.42408</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.32276</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.31623</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.33536</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.33528</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.35834</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.32349</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36608</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.33607</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.33295</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.33041</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.31521</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.31282</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.31291</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.29944</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.28941</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.30721</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.31744</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.31772</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.45177</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.42754</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.35536</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.3552</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.3622</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.40591</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.32767</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.36342</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34114</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.35667</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>-0.00626</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.24288</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.32399</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.34837</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.34765</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.33793</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32967</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.32341</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.27513</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.03362</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.28656</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.22275</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.2843</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.30766</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.30664</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.21419</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.27608</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.30371</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.30314</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.29767</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.30305</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.30831</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.30555</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.34716</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.30574</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.32358</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.33311</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.32093</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.32267</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.5313600000000001</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6438400000000001</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.32746</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.32271</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.32424</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.40584</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.39577</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.3875</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.31671</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.27449</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.29171</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.29601</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.31565</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.31664</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.30773</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33734</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.01391</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.27981</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.28712</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33734</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.28057</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.28759</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3509</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.29468</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.33276</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.32653</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.28574</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.18665</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.36177</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.31942</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.28604</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.00014</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.28532</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.30074</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.29436</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.32607</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.20193</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.05046</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.25212</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.004030000000000001</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.04973</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.3891</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>-0.04006000000000001</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.2096</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.2078</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>-0.04040999999999999</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>-0.02114</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.01994</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.00554</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>-0.0354</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>-0.04292</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>-0.02471</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.20055</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.19939</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.20088</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.20072</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>-0.03831</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.29807</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.27203</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.21903</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.24129</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>-0.0294</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.1504</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.38886</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.29552</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37947</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>-0.00358</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>-0.01156</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>-0.01515</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>-0.01412</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.07576000000000001</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.05627</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>-0.00433</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.2839100000000001</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.17318</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.00622</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>-0.04995</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.00731</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>-0.03442</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>-0.04238</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>-0.01887</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>-0.01989</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>-0.02064</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.11665</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.2844</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.18381</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.11939</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.18675</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.27725</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.20081</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.17464</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.01275</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.24422</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.00907</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.0094</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.17485</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.00143</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.20624</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.27932</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.17367</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.0081</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.1639</v>
+      </c>
+      <c r="U135" t="n">
+        <v>-5e-05</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.00024</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.16615</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.16895</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.17176</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.00711</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.17457</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.00694</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.01711</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.18583</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.18762</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.15612</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.24007</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.03886999999999999</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.2523</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.06185</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.19993</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.10846</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.14569</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.26297</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.02559</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.28399</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.30371</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.24575</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.19994</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.16185</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.00213</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.00445</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.00262</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.00011</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.01757</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.21832</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.20273</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.13397</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.009789999999999998</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.00907</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>-0.008659999999999999</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>-0.01469</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>-0.00534</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.00256</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>-0.01699</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>-0.00422</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.00256</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.15219</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.14804</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.00086</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.20128</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.15246</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.17438</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.02453</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.11681</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.15456</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.00457</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>-0.04879</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.02509</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.004589999999999999</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>-0.0437</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.22576</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.06042</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.02549</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.0313</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.20908</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.2293</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.22581</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.09764</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.10919</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.2295</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.07817</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.20673</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.02896</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.02386</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.19818</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.21438</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.23512</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.2527</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.28028</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.27572</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.05321</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.19028</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.18724</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.26854</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.00149</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.20616</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.2264</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.21829</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.04185</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.0125</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.00075</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.00074</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.00019</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.00019</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.0005200000000000001</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.20085</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.00019</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.00023</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.18094</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.01249</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.01249</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30574</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.00176</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.00341</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24562</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.03671</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.00628</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00035</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>-0.04845</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02203</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.04045</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04297</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04089</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02936</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04393</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.04903</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.22576</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04932</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.1014</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.20619</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.20802</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.21358</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.20914</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.21141</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.00141</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.19084</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.24568</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.30427</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.30076</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.29449</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28256</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29588</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30108</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.25846</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29629</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.28601</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.29338</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.24819</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.22096</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.29744</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.27801</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.30141</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.29207</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.29639</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.30108</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.24024</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.30025</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29968</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.27239</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.35818</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.30361</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.03305</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.28425</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.30949</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.29187</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.28308</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.17718</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.1717</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.17616</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.17345</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.02054</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.16944</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.15798</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.01964</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.04898</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.02206</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.01929</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.008529999999999999</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.01074</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.01463</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.20058</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.20031</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.04905</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>-0.04917</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.04744</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.33911</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.85064</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.86178</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.09272</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.00014</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.25092</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.31882</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.2804</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29578</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.29658</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.04720000000000001</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.4684</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.29808</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29242</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00229</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.31264</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06881</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.30701</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30254</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30719</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30802</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25453</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47501</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.31663</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.65164</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.5010599999999999</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.37818</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.43194</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.73078</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.82004</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.39112</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.56167</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.4343399999999999</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.58287</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.7003400000000001</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.69857</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.70164</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.7760199999999999</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37653</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.42797</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.38536</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.31052</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.43702</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.31444</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.29626</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.27662</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.26977</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.19933</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.26274</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.25808</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.25122</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.22042</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.26877</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.20813</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.17461</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.20362</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.16893</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.17169</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.02109</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.16723</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.18987</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.23869</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.31963</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.29148</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.24734</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.25702</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.25626</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.27848</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.35637</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.33247</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.32359</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.38213</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.30774</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.32959</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.29499</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.31203</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30747</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30852</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.2585</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31121</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30238</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30213</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31905</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32351</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31315</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.31913</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.32284</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.31797</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.33408</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.36976</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.34795</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.32317</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39857</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.32561</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.31426</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.33305</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.29863</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.29398</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.29441</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36151</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.3552</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.33522</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.33617</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33365</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32522</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.31555</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32751</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.31552</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.30423</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.30393</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.29636</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.30219</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.30226</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.30393</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.31451</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.30952</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.31523</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.31476</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.32121</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.31099</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.32979</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.15533</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31115</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.31942</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.32463</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.33258</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33291</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.33395</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29655</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32404</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.44623</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.41009</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.44301</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.26472</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.70896</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.7413500000000001</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.40775</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.4397799999999999</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.50113</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.6430800000000001</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.74441</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.41463</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.35102</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.35369</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.34835</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.42825</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.35261</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.34713</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35698</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.33409</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.20301</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.31883</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.38297</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.31785</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.31711</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34697</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.32371</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.32223</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.31662</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.31754</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.30743</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.30243</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.30656</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.30187</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.29983</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.29593</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.29626</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.30711</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.31198</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.30619</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.3173</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.36218</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39098</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.34633</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35367</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43461</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37966</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.34383</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35609</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33673</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.36554</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.34202</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.35308</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.34161</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.34294</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33966</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.36387</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.35285</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.34918</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.38435</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.37143</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.25965</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.53811</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.29727</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.29782</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.28244</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.31414</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.21151</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.7101900000000001</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.6283099999999999</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.54303</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.34087</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.39358</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.32342</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.28496</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.33203</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.31229</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33163</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.28663</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.29832</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.29203</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.30933</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.30364</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.30405</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.02147</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.29047</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.29146</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.28629</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31548</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.32875</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.28526</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35743</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30703</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30536</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.31495</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.31145</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32828</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32715</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.35801</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.38132</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.27236</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.43345</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.39489</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.34484</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.34634</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.20026</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32983</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.2996</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.43549</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.5435800000000001</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.30402</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.31121</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.32556</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.32245</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.32697</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.10473</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.14164</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.44315</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.31024</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.31261</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.32905</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.34103</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.34105</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.3276</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.6464500000000001</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.41242</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.40592</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33826</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.33579</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.33661</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33697</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.33111</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.33231</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33385</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.32547</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32647</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33692</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.33895</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33525</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.35268</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35421</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34754</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33416</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.29306</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.32597</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.18846</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.30231</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.27712</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.30714</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.30697</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.30178</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.30544</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.33916</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.31393</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.33257</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.28731</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>-0.04765</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.14774</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.26318</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.33536</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.37603</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.17788</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.07026</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.33514</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.33534</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.35743</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.34393</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33737</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.3395</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34842</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="E143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F143" t="n">
+        <v>-0.04983</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.23012</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.32975</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33279</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.33296</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34299</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33841</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33696</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33395</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33166</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30586</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31853</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30971</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17608</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30462</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29569</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.3117</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14574</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19863</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14611</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28757</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.0476</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12158</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33333</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22599</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26022</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14395</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14528</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28367</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18818</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.26721</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22681</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>-0.04898</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>-0.04944</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.22823</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.08563</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.2002</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.02067</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.1979</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.09927</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.21424</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.2663</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.19817</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.11809</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.07803</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>-0.00315</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.24337</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.31279</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.41001</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.39389</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33203</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.15907</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>-0.03408</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.27537</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.25468</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>-0.02533</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>-0.04753</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.25406</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.32384</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.34383</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.34449</v>
       </c>
     </row>
   </sheetData>
